--- a/public/sample-ar-worklist.xlsx
+++ b/public/sample-ar-worklist.xlsx
@@ -75,17 +75,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-4471-08</t>
+          <t>K-6120-33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Delgado, Ricardo M</t>
+          <t>Hartley, Denise R</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD77140228</t>
+          <t>MD20447715</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -122,7 +122,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B-2290-15</t>
+          <t>L-7741-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -169,7 +169,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C-8812-02</t>
+          <t>M-3308-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
